--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/96.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/96.xlsx
@@ -426,13 +426,13 @@
         <v>-2.936103667505625</v>
       </c>
       <c r="E2">
-        <v>-5.463182543544258</v>
+        <v>-6.033057129057957</v>
       </c>
       <c r="F2">
-        <v>0.6009812318509363</v>
+        <v>-0.7245557187607765</v>
       </c>
       <c r="G2">
-        <v>-10.82281244010054</v>
+        <v>-11.76945015362608</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.723519817554857</v>
       </c>
       <c r="E3">
-        <v>-6.694240065548011</v>
+        <v>-6.909355646117506</v>
       </c>
       <c r="F3">
-        <v>0.283843256791354</v>
+        <v>-0.660703502618185</v>
       </c>
       <c r="G3">
-        <v>-10.7482639336736</v>
+        <v>-11.18579339820909</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.534128899642338</v>
       </c>
       <c r="E4">
-        <v>-7.270593660728442</v>
+        <v>-7.459876266857504</v>
       </c>
       <c r="F4">
-        <v>0.3447779629412857</v>
+        <v>-0.6423998964859271</v>
       </c>
       <c r="G4">
-        <v>-9.928537125466665</v>
+        <v>-11.14212869492272</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.391739265946776</v>
       </c>
       <c r="E5">
-        <v>-7.454963017860231</v>
+        <v>-8.547025016455947</v>
       </c>
       <c r="F5">
-        <v>0.864716845554243</v>
+        <v>-0.3607152178987609</v>
       </c>
       <c r="G5">
-        <v>-10.69700065825479</v>
+        <v>-10.70280695422543</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.284689914245777</v>
       </c>
       <c r="E6">
-        <v>-9.318496479676822</v>
+        <v>-9.687206121461127</v>
       </c>
       <c r="F6">
-        <v>1.246042525554551</v>
+        <v>-0.3801139257375197</v>
       </c>
       <c r="G6">
-        <v>-9.674063934053967</v>
+        <v>-10.33074582642899</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.203913151712137</v>
       </c>
       <c r="E7">
-        <v>-8.655137260452559</v>
+        <v>-10.54213636625443</v>
       </c>
       <c r="F7">
-        <v>0.7062998634428655</v>
+        <v>0.1541051825322983</v>
       </c>
       <c r="G7">
-        <v>-9.398742641708933</v>
+        <v>-10.3735750914462</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.127655075094404</v>
       </c>
       <c r="E8">
-        <v>-10.51156457769237</v>
+        <v>-11.16931280841679</v>
       </c>
       <c r="F8">
-        <v>1.129357036461407</v>
+        <v>0.1619746728588936</v>
       </c>
       <c r="G8">
-        <v>-8.635193835613578</v>
+        <v>-9.925934213109326</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.037218715224784</v>
       </c>
       <c r="E9">
-        <v>-11.09450101282265</v>
+        <v>-12.39448522997326</v>
       </c>
       <c r="F9">
-        <v>1.376475600064555</v>
+        <v>0.4260789100564459</v>
       </c>
       <c r="G9">
-        <v>-8.568555885297705</v>
+        <v>-9.264658715626242</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.913652257425094</v>
       </c>
       <c r="E10">
-        <v>-12.20720031849144</v>
+        <v>-13.17033002471918</v>
       </c>
       <c r="F10">
-        <v>1.521178131455184</v>
+        <v>0.5681066431034352</v>
       </c>
       <c r="G10">
-        <v>-8.317284772126008</v>
+        <v>-9.014708639217647</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.750453411020565</v>
       </c>
       <c r="E11">
-        <v>-13.30772656176716</v>
+        <v>-14.27645064364944</v>
       </c>
       <c r="F11">
-        <v>1.617681277146521</v>
+        <v>0.527208487692418</v>
       </c>
       <c r="G11">
-        <v>-7.646647144539191</v>
+        <v>-8.434705620855919</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.553251995195682</v>
       </c>
       <c r="E12">
-        <v>-14.42262706943811</v>
+        <v>-14.96317582978719</v>
       </c>
       <c r="F12">
-        <v>2.021132650475603</v>
+        <v>0.5612958063176177</v>
       </c>
       <c r="G12">
-        <v>-6.511967941094126</v>
+        <v>-7.970366420114283</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.333822711265901</v>
       </c>
       <c r="E13">
-        <v>-14.83077560596298</v>
+        <v>-16.50625996541399</v>
       </c>
       <c r="F13">
-        <v>2.156641960429963</v>
+        <v>0.7881110848781503</v>
       </c>
       <c r="G13">
-        <v>-6.613724322277357</v>
+        <v>-7.875715180335766</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.107918650522304</v>
       </c>
       <c r="E14">
-        <v>-16.26261597625425</v>
+        <v>-17.69051494899825</v>
       </c>
       <c r="F14">
-        <v>2.114640419638417</v>
+        <v>1.039310186307489</v>
       </c>
       <c r="G14">
-        <v>-6.615353426902212</v>
+        <v>-6.939691448945398</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.8845236239388418</v>
       </c>
       <c r="E15">
-        <v>-16.44297748445758</v>
+        <v>-18.27412005115183</v>
       </c>
       <c r="F15">
-        <v>2.522117658545105</v>
+        <v>0.9075301864005326</v>
       </c>
       <c r="G15">
-        <v>-5.244219085840017</v>
+        <v>-6.154319428812926</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.6675740881506739</v>
       </c>
       <c r="E16">
-        <v>-17.38471815236245</v>
+        <v>-19.64232491752407</v>
       </c>
       <c r="F16">
-        <v>3.081351805644662</v>
+        <v>1.261062483302111</v>
       </c>
       <c r="G16">
-        <v>-4.288133087639238</v>
+        <v>-5.524414638336659</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.4591435179969978</v>
       </c>
       <c r="E17">
-        <v>-19.34829832178283</v>
+        <v>-20.33813317682922</v>
       </c>
       <c r="F17">
-        <v>3.260984933676541</v>
+        <v>1.39255918155731</v>
       </c>
       <c r="G17">
-        <v>-4.453662126949594</v>
+        <v>-5.127234231456821</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.2577201616103393</v>
       </c>
       <c r="E18">
-        <v>-18.82746900880404</v>
+        <v>-20.60795070375803</v>
       </c>
       <c r="F18">
-        <v>2.863335445636666</v>
+        <v>1.569604489822843</v>
       </c>
       <c r="G18">
-        <v>-2.899399717288348</v>
+        <v>-4.733638376900583</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.06415279470992172</v>
       </c>
       <c r="E19">
-        <v>-19.6464947416942</v>
+        <v>-22.12337445196147</v>
       </c>
       <c r="F19">
-        <v>3.441146560111406</v>
+        <v>1.685511313557355</v>
       </c>
       <c r="G19">
-        <v>-2.953650989891682</v>
+        <v>-4.302364256405396</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.1190556742597886</v>
       </c>
       <c r="E20">
-        <v>-21.13355205654906</v>
+        <v>-22.54809845488374</v>
       </c>
       <c r="F20">
-        <v>3.776313951692919</v>
+        <v>2.225063451166397</v>
       </c>
       <c r="G20">
-        <v>-3.148229784267355</v>
+        <v>-3.368119747453872</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.2889134879776408</v>
       </c>
       <c r="E21">
-        <v>-22.92550907439356</v>
+        <v>-23.62540409364234</v>
       </c>
       <c r="F21">
-        <v>4.384058950635221</v>
+        <v>2.420447156995105</v>
       </c>
       <c r="G21">
-        <v>-3.067808407882702</v>
+        <v>-2.995566494302006</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.4384822202150487</v>
       </c>
       <c r="E22">
-        <v>-22.06737670366881</v>
+        <v>-23.69382825021889</v>
       </c>
       <c r="F22">
-        <v>3.691898343143233</v>
+        <v>2.522987444318045</v>
       </c>
       <c r="G22">
-        <v>-2.295910440584966</v>
+        <v>-2.845675815092419</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.5598698441228656</v>
       </c>
       <c r="E23">
-        <v>-22.00898255244172</v>
+        <v>-23.8758261236842</v>
       </c>
       <c r="F23">
-        <v>4.30218974348174</v>
+        <v>2.777070921043931</v>
       </c>
       <c r="G23">
-        <v>-1.665264198644822</v>
+        <v>-2.581497180662257</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.6434772660943775</v>
       </c>
       <c r="E24">
-        <v>-22.61111513031536</v>
+        <v>-24.48548016726711</v>
       </c>
       <c r="F24">
-        <v>4.853294292890223</v>
+        <v>2.7928330959844</v>
       </c>
       <c r="G24">
-        <v>-2.199613126341752</v>
+        <v>-2.703865390392327</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.679297355372957</v>
       </c>
       <c r="E25">
-        <v>-23.31470235443191</v>
+        <v>-24.70937148336596</v>
       </c>
       <c r="F25">
-        <v>4.606737362386172</v>
+        <v>3.293244873811165</v>
       </c>
       <c r="G25">
-        <v>-2.204889441160392</v>
+        <v>-2.609768933839423</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.6588029703715045</v>
       </c>
       <c r="E26">
-        <v>-23.28148497025593</v>
+        <v>-24.60053242738751</v>
       </c>
       <c r="F26">
-        <v>4.434672198946271</v>
+        <v>3.330957128191015</v>
       </c>
       <c r="G26">
-        <v>-1.884177743354263</v>
+        <v>-2.4651180190242</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.5770697083961971</v>
       </c>
       <c r="E27">
-        <v>-23.30601383634037</v>
+        <v>-25.2388394759004</v>
       </c>
       <c r="F27">
-        <v>4.401431471806732</v>
+        <v>3.082080768959126</v>
       </c>
       <c r="G27">
-        <v>-1.962220731416412</v>
+        <v>-3.2264503029617</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.4332238100668482</v>
       </c>
       <c r="E28">
-        <v>-23.22397129982971</v>
+        <v>-25.11340003425661</v>
       </c>
       <c r="F28">
-        <v>4.639341903360362</v>
+        <v>3.171991766858985</v>
       </c>
       <c r="G28">
-        <v>-1.694903981987732</v>
+        <v>-3.106476146021681</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.231953050043672</v>
       </c>
       <c r="E29">
-        <v>-23.34258701526681</v>
+        <v>-24.82495535453594</v>
       </c>
       <c r="F29">
-        <v>4.404846002241071</v>
+        <v>3.264889857613338</v>
       </c>
       <c r="G29">
-        <v>-2.241061307470266</v>
+        <v>-3.230543950480566</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.01478385013431138</v>
       </c>
       <c r="E30">
-        <v>-22.40786942771222</v>
+        <v>-24.39618197057197</v>
       </c>
       <c r="F30">
-        <v>4.932181377393626</v>
+        <v>3.071210931899591</v>
       </c>
       <c r="G30">
-        <v>-2.141531891423255</v>
+        <v>-3.754118335249971</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.2916322632221221</v>
       </c>
       <c r="E31">
-        <v>-21.54763968526844</v>
+        <v>-24.20560771572088</v>
       </c>
       <c r="F31">
-        <v>5.180946735393539</v>
+        <v>3.407730219082473</v>
       </c>
       <c r="G31">
-        <v>-2.409253306263558</v>
+        <v>-3.637266628840923</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.5807340347591625</v>
       </c>
       <c r="E32">
-        <v>-22.39563406714928</v>
+        <v>-24.53139391846308</v>
       </c>
       <c r="F32">
-        <v>4.673995825289076</v>
+        <v>3.088278613866872</v>
       </c>
       <c r="G32">
-        <v>-3.437962386755335</v>
+        <v>-4.334244058607481</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.8638022164577052</v>
       </c>
       <c r="E33">
-        <v>-21.64596696338375</v>
+        <v>-23.82448827849799</v>
       </c>
       <c r="F33">
-        <v>4.99443650118362</v>
+        <v>3.226195159493767</v>
       </c>
       <c r="G33">
-        <v>-3.129735269583909</v>
+        <v>-4.351986678848687</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.125173938945565</v>
       </c>
       <c r="E34">
-        <v>-20.80709303357224</v>
+        <v>-23.55647739849548</v>
       </c>
       <c r="F34">
-        <v>4.779233276875531</v>
+        <v>3.095241870254804</v>
       </c>
       <c r="G34">
-        <v>-2.999738464158605</v>
+        <v>-3.956967968490291</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.35023879452345</v>
       </c>
       <c r="E35">
-        <v>-20.03003965433079</v>
+        <v>-22.95671215107699</v>
       </c>
       <c r="F35">
-        <v>4.699961829897229</v>
+        <v>3.337357094745044</v>
       </c>
       <c r="G35">
-        <v>-3.177253431886762</v>
+        <v>-4.510813936793655</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.530041244984325</v>
       </c>
       <c r="E36">
-        <v>-20.29295869724906</v>
+        <v>-22.19875939071843</v>
       </c>
       <c r="F36">
-        <v>4.375364406375438</v>
+        <v>3.272525748332344</v>
       </c>
       <c r="G36">
-        <v>-3.032701725366001</v>
+        <v>-5.099565560280203</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.661252540443358</v>
       </c>
       <c r="E37">
-        <v>-19.83402053943286</v>
+        <v>-21.60526549240043</v>
       </c>
       <c r="F37">
-        <v>4.767936002236151</v>
+        <v>3.10817434214731</v>
       </c>
       <c r="G37">
-        <v>-3.689491963641553</v>
+        <v>-5.081702845787806</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.742468060400858</v>
       </c>
       <c r="E38">
-        <v>-18.99341472049889</v>
+        <v>-21.42385737494325</v>
       </c>
       <c r="F38">
-        <v>4.760144378445418</v>
+        <v>3.097105696911103</v>
       </c>
       <c r="G38">
-        <v>-3.953284207872231</v>
+        <v>-5.067552610103972</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.779078554076803</v>
       </c>
       <c r="E39">
-        <v>-18.84669837723799</v>
+        <v>-20.81810735000568</v>
       </c>
       <c r="F39">
-        <v>4.003775356827635</v>
+        <v>3.11577875490501</v>
       </c>
       <c r="G39">
-        <v>-3.684445394346931</v>
+        <v>-5.047092204743417</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.778495626055185</v>
       </c>
       <c r="E40">
-        <v>-18.94907918960634</v>
+        <v>-19.66043707211165</v>
       </c>
       <c r="F40">
-        <v>4.05180409884195</v>
+        <v>3.18619661108219</v>
       </c>
       <c r="G40">
-        <v>-3.896336036106276</v>
+        <v>-5.537622395223101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.749809992433849</v>
       </c>
       <c r="E41">
-        <v>-17.50808514155516</v>
+        <v>-19.1814015246946</v>
       </c>
       <c r="F41">
-        <v>4.529256845732724</v>
+        <v>2.950726549897209</v>
       </c>
       <c r="G41">
-        <v>-3.579764979221653</v>
+        <v>-5.51257491161596</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.706653710570228</v>
       </c>
       <c r="E42">
-        <v>-16.86800051859523</v>
+        <v>-18.85720184867849</v>
       </c>
       <c r="F42">
-        <v>4.317299164908803</v>
+        <v>3.063493861175111</v>
       </c>
       <c r="G42">
-        <v>-4.172417055127324</v>
+        <v>-5.165278001638525</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.662304235350027</v>
       </c>
       <c r="E43">
-        <v>-16.56090376681476</v>
+        <v>-18.09973086083361</v>
       </c>
       <c r="F43">
-        <v>4.578201762094536</v>
+        <v>2.898319057791695</v>
       </c>
       <c r="G43">
-        <v>-4.481873833001164</v>
+        <v>-5.137463128764804</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.630445967217728</v>
       </c>
       <c r="E44">
-        <v>-16.27021219976736</v>
+        <v>-17.48132600098928</v>
       </c>
       <c r="F44">
-        <v>4.290590943107741</v>
+        <v>2.903942015721898</v>
       </c>
       <c r="G44">
-        <v>-4.182071588625261</v>
+        <v>-5.878175751921692</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.620750870331898</v>
       </c>
       <c r="E45">
-        <v>-15.3778366016694</v>
+        <v>-16.87543061365535</v>
       </c>
       <c r="F45">
-        <v>4.071582198951192</v>
+        <v>3.046277073075326</v>
       </c>
       <c r="G45">
-        <v>-3.668136072886246</v>
+        <v>-5.838959757418579</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.638149373142552</v>
       </c>
       <c r="E46">
-        <v>-14.29507364322997</v>
+        <v>-16.59844879719121</v>
       </c>
       <c r="F46">
-        <v>4.411640271678833</v>
+        <v>2.760218614601378</v>
       </c>
       <c r="G46">
-        <v>-4.419080204095708</v>
+        <v>-5.996215347119697</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.686441021979109</v>
       </c>
       <c r="E47">
-        <v>-15.13346580052781</v>
+        <v>-15.09416811497228</v>
       </c>
       <c r="F47">
-        <v>4.229752327576534</v>
+        <v>2.874140670038783</v>
       </c>
       <c r="G47">
-        <v>-3.720617260656805</v>
+        <v>-6.435963944557636</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.76518814705235</v>
       </c>
       <c r="E48">
-        <v>-13.15552797955749</v>
+        <v>-14.76170770163109</v>
       </c>
       <c r="F48">
-        <v>4.48735967923393</v>
+        <v>2.591312844435753</v>
       </c>
       <c r="G48">
-        <v>-4.472932032776601</v>
+        <v>-6.447722738196011</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.872353942961363</v>
       </c>
       <c r="E49">
-        <v>-13.43099387388807</v>
+        <v>-14.81491033870214</v>
       </c>
       <c r="F49">
-        <v>4.164326213368624</v>
+        <v>2.480034937748084</v>
       </c>
       <c r="G49">
-        <v>-4.638035520718605</v>
+        <v>-6.759826811085239</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.005178612096925</v>
       </c>
       <c r="E50">
-        <v>-12.79343440341364</v>
+        <v>-13.5379889040383</v>
       </c>
       <c r="F50">
-        <v>3.911274882426626</v>
+        <v>2.586024546936281</v>
       </c>
       <c r="G50">
-        <v>-4.154272380219087</v>
+        <v>-6.66684514247274</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.158288615883494</v>
       </c>
       <c r="E51">
-        <v>-12.75947774762184</v>
+        <v>-13.17746108856391</v>
       </c>
       <c r="F51">
-        <v>3.809372438003841</v>
+        <v>2.749133402017115</v>
       </c>
       <c r="G51">
-        <v>-4.996673505199837</v>
+        <v>-7.030198131685522</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.329709841104626</v>
       </c>
       <c r="E52">
-        <v>-11.12849504751638</v>
+        <v>-11.97705426613739</v>
       </c>
       <c r="F52">
-        <v>3.692491454203637</v>
+        <v>2.586370804510651</v>
       </c>
       <c r="G52">
-        <v>-5.33809885059186</v>
+        <v>-6.960689667691722</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.518472873585569</v>
       </c>
       <c r="E53">
-        <v>-11.50962279116192</v>
+        <v>-11.52062464796139</v>
       </c>
       <c r="F53">
-        <v>3.640809611942976</v>
+        <v>2.516956929625664</v>
       </c>
       <c r="G53">
-        <v>-5.247304985946712</v>
+        <v>-6.937427933384902</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.722988092598317</v>
       </c>
       <c r="E54">
-        <v>-11.03864447371503</v>
+        <v>-10.64093711046078</v>
       </c>
       <c r="F54">
-        <v>3.95572010705643</v>
+        <v>2.360377266413696</v>
       </c>
       <c r="G54">
-        <v>-5.048058180242129</v>
+        <v>-7.392415447001171</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.946995497844667</v>
       </c>
       <c r="E55">
-        <v>-10.92482987056943</v>
+        <v>-10.6944013998453</v>
       </c>
       <c r="F55">
-        <v>3.863768011876074</v>
+        <v>2.367224551365237</v>
       </c>
       <c r="G55">
-        <v>-5.624061537890271</v>
+        <v>-7.552195626721895</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.191378932255489</v>
       </c>
       <c r="E56">
-        <v>-9.281491366772601</v>
+        <v>-9.66654804833143</v>
       </c>
       <c r="F56">
-        <v>3.533754722274779</v>
+        <v>2.01174890453669</v>
       </c>
       <c r="G56">
-        <v>-5.349014373727304</v>
+        <v>-7.489905871522523</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.457525207056162</v>
       </c>
       <c r="E57">
-        <v>-9.831139813134385</v>
+        <v>-9.372999071892549</v>
       </c>
       <c r="F57">
-        <v>4.009661735591928</v>
+        <v>2.061416157273743</v>
       </c>
       <c r="G57">
-        <v>-5.157437935631411</v>
+        <v>-8.048083065102544</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.748397807783991</v>
       </c>
       <c r="E58">
-        <v>-7.753620444228652</v>
+        <v>-9.400410266636417</v>
       </c>
       <c r="F58">
-        <v>3.670672256813898</v>
+        <v>1.932185872232604</v>
       </c>
       <c r="G58">
-        <v>-6.822424634146363</v>
+        <v>-8.035039785125342</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.060710825168211</v>
       </c>
       <c r="E59">
-        <v>-8.174938813864559</v>
+        <v>-8.124481449479216</v>
       </c>
       <c r="F59">
-        <v>3.927303791670796</v>
+        <v>1.745612682100071</v>
       </c>
       <c r="G59">
-        <v>-6.642956829464053</v>
+        <v>-8.633289297434359</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.392448499776528</v>
       </c>
       <c r="E60">
-        <v>-7.299778276708013</v>
+        <v>-7.915770120772607</v>
       </c>
       <c r="F60">
-        <v>3.595976711368661</v>
+        <v>1.80259938920826</v>
       </c>
       <c r="G60">
-        <v>-6.923254200999748</v>
+        <v>-8.624092949612162</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.737102829367915</v>
       </c>
       <c r="E61">
-        <v>-7.482199777728456</v>
+        <v>-7.544772059548324</v>
       </c>
       <c r="F61">
-        <v>3.637264199458994</v>
+        <v>1.739370105352574</v>
       </c>
       <c r="G61">
-        <v>-6.705392786360528</v>
+        <v>-8.781024806983982</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.083359906485041</v>
       </c>
       <c r="E62">
-        <v>-6.823695662542917</v>
+        <v>-7.541790053817096</v>
       </c>
       <c r="F62">
-        <v>3.658304731490101</v>
+        <v>1.523744413669057</v>
       </c>
       <c r="G62">
-        <v>-6.630775095201918</v>
+        <v>-9.175768083788016</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.422162475991405</v>
       </c>
       <c r="E63">
-        <v>-6.51550246297269</v>
+        <v>-7.085742531082974</v>
       </c>
       <c r="F63">
-        <v>3.496175006679377</v>
+        <v>1.565315203411147</v>
       </c>
       <c r="G63">
-        <v>-6.713428658211974</v>
+        <v>-9.186464304377807</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.737363766834928</v>
       </c>
       <c r="E64">
-        <v>-6.867748775065373</v>
+        <v>-6.282025535136129</v>
       </c>
       <c r="F64">
-        <v>3.366060025252047</v>
+        <v>1.606430391081698</v>
       </c>
       <c r="G64">
-        <v>-7.192314927815293</v>
+        <v>-9.407312410829261</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.014501420114089</v>
       </c>
       <c r="E65">
-        <v>-5.691800214130771</v>
+        <v>-5.846486569924009</v>
       </c>
       <c r="F65">
-        <v>3.093326684819532</v>
+        <v>1.544342597507069</v>
       </c>
       <c r="G65">
-        <v>-6.913093183051136</v>
+        <v>-9.285265322683898</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.240996230896419</v>
       </c>
       <c r="E66">
-        <v>-6.219935025829942</v>
+        <v>-6.431536989618632</v>
       </c>
       <c r="F66">
-        <v>3.176723401463775</v>
+        <v>1.6077922270919</v>
       </c>
       <c r="G66">
-        <v>-7.337114655072209</v>
+        <v>-9.431623664461709</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.404388270005863</v>
       </c>
       <c r="E67">
-        <v>-6.525059002231121</v>
+        <v>-6.171130639551881</v>
       </c>
       <c r="F67">
-        <v>3.346025131247938</v>
+        <v>1.390902446751711</v>
       </c>
       <c r="G67">
-        <v>-7.223797896839528</v>
+        <v>-9.630893966867612</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.497154987191619</v>
       </c>
       <c r="E68">
-        <v>-6.055376486717585</v>
+        <v>-6.420447915381339</v>
       </c>
       <c r="F68">
-        <v>3.20059197980804</v>
+        <v>1.313675410523519</v>
       </c>
       <c r="G68">
-        <v>-6.415728063231917</v>
+        <v>-9.531077368915579</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.510891811741467</v>
       </c>
       <c r="E69">
-        <v>-5.457770909188007</v>
+        <v>-6.698887509020494</v>
       </c>
       <c r="F69">
-        <v>3.40851054117591</v>
+        <v>0.9853586173631573</v>
       </c>
       <c r="G69">
-        <v>-7.404260395211051</v>
+        <v>-9.318577118294208</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.442752533659556</v>
       </c>
       <c r="E70">
-        <v>-5.946051505014124</v>
+        <v>-6.244256231348138</v>
       </c>
       <c r="F70">
-        <v>2.826133465576941</v>
+        <v>1.406141093493611</v>
       </c>
       <c r="G70">
-        <v>-7.319862854814132</v>
+        <v>-9.46409218956909</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.296269158623764</v>
       </c>
       <c r="E71">
-        <v>-6.401355602921102</v>
+        <v>-6.39015439197804</v>
       </c>
       <c r="F71">
-        <v>2.842982458549882</v>
+        <v>1.09319051565518</v>
       </c>
       <c r="G71">
-        <v>-7.951163088274349</v>
+        <v>-8.837872465083178</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.077236613865365</v>
       </c>
       <c r="E72">
-        <v>-6.887385158209162</v>
+        <v>-6.824052838716852</v>
       </c>
       <c r="F72">
-        <v>2.725304585308185</v>
+        <v>1.301475215415088</v>
       </c>
       <c r="G72">
-        <v>-7.195604466000096</v>
+        <v>-9.398575554055101</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.79856512422688</v>
       </c>
       <c r="E73">
-        <v>-6.373068080587696</v>
+        <v>-6.603625300862902</v>
       </c>
       <c r="F73">
-        <v>2.924879830195058</v>
+        <v>1.328132078437176</v>
       </c>
       <c r="G73">
-        <v>-6.963441392490756</v>
+        <v>-8.657567916759417</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.472155225220737</v>
       </c>
       <c r="E74">
-        <v>-7.647327306792315</v>
+        <v>-6.330634720481922</v>
       </c>
       <c r="F74">
-        <v>2.60106769897112</v>
+        <v>1.038617671158749</v>
       </c>
       <c r="G74">
-        <v>-5.997546826861164</v>
+        <v>-8.285269211205186</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.113158079445527</v>
       </c>
       <c r="E75">
-        <v>-6.570910455257228</v>
+        <v>-7.2074233164778</v>
       </c>
       <c r="F75">
-        <v>2.844952316233739</v>
+        <v>1.076727541891943</v>
       </c>
       <c r="G75">
-        <v>-6.515792681920107</v>
+        <v>-8.139553112596788</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.735968446845527</v>
       </c>
       <c r="E76">
-        <v>-7.935568479158065</v>
+        <v>-7.947276381882757</v>
       </c>
       <c r="F76">
-        <v>2.421919994237282</v>
+        <v>1.074124811512347</v>
       </c>
       <c r="G76">
-        <v>-6.740588234193325</v>
+        <v>-7.997777932948677</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.348870346410851</v>
       </c>
       <c r="E77">
-        <v>-8.746541135289386</v>
+        <v>-8.383928407729931</v>
       </c>
       <c r="F77">
-        <v>2.585545750577463</v>
+        <v>1.071295108464384</v>
       </c>
       <c r="G77">
-        <v>-6.238800513036761</v>
+        <v>-7.829046815397321</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.962552578412463</v>
       </c>
       <c r="E78">
-        <v>-7.824017376184496</v>
+        <v>-8.666238794323826</v>
       </c>
       <c r="F78">
-        <v>2.595955015361042</v>
+        <v>1.015827627172929</v>
       </c>
       <c r="G78">
-        <v>-5.736018098190982</v>
+        <v>-7.463477304026683</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.579949288251735</v>
       </c>
       <c r="E79">
-        <v>-8.291054296084114</v>
+        <v>-9.180713693975637</v>
       </c>
       <c r="F79">
-        <v>2.439420083988825</v>
+        <v>1.136668207158515</v>
       </c>
       <c r="G79">
-        <v>-5.441844619153519</v>
+        <v>-6.702776820280231</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.200642036849749</v>
       </c>
       <c r="E80">
-        <v>-10.35487222082924</v>
+        <v>-9.271029427445358</v>
       </c>
       <c r="F80">
-        <v>2.934023349587159</v>
+        <v>1.062048871514336</v>
       </c>
       <c r="G80">
-        <v>-5.928268108391382</v>
+        <v>-6.784516622683397</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.825467392528604</v>
       </c>
       <c r="E81">
-        <v>-10.91033100983446</v>
+        <v>-10.58456557314888</v>
       </c>
       <c r="F81">
-        <v>2.32820844669338</v>
+        <v>1.169022581177058</v>
       </c>
       <c r="G81">
-        <v>-4.906592373828064</v>
+        <v>-6.566313200502741</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.449177125191516</v>
       </c>
       <c r="E82">
-        <v>-11.59511664628351</v>
+        <v>-11.47682488132975</v>
       </c>
       <c r="F82">
-        <v>2.86644348013197</v>
+        <v>0.9531185580462006</v>
       </c>
       <c r="G82">
-        <v>-3.692664018319756</v>
+        <v>-6.056886440672578</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.073371108896265</v>
       </c>
       <c r="E83">
-        <v>-12.17558192067552</v>
+        <v>-12.4171908362861</v>
       </c>
       <c r="F83">
-        <v>2.289866633087402</v>
+        <v>1.000579040022195</v>
       </c>
       <c r="G83">
-        <v>-4.537861250757588</v>
+        <v>-5.595586146634998</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.699883218651042</v>
       </c>
       <c r="E84">
-        <v>-13.84187107025336</v>
+        <v>-13.75803019323904</v>
       </c>
       <c r="F84">
-        <v>2.473992825912065</v>
+        <v>0.9501496892745672</v>
       </c>
       <c r="G84">
-        <v>-3.842659127312987</v>
+        <v>-5.159555249494804</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.331186100854529</v>
       </c>
       <c r="E85">
-        <v>-14.787303943026</v>
+        <v>-14.53852243145745</v>
       </c>
       <c r="F85">
-        <v>2.721114702984825</v>
+        <v>0.9178483307698032</v>
       </c>
       <c r="G85">
-        <v>-4.526627216782028</v>
+        <v>-5.314578652570519</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.9777380287380073</v>
       </c>
       <c r="E86">
-        <v>-15.04180442658885</v>
+        <v>-15.65713175684147</v>
       </c>
       <c r="F86">
-        <v>2.249579812819651</v>
+        <v>1.070175155735799</v>
       </c>
       <c r="G86">
-        <v>-3.819368674815665</v>
+        <v>-4.86652788733284</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.6484226932279931</v>
       </c>
       <c r="E87">
-        <v>-17.39459448889289</v>
+        <v>-16.48776986859585</v>
       </c>
       <c r="F87">
-        <v>2.533519307477238</v>
+        <v>0.8957524586675293</v>
       </c>
       <c r="G87">
-        <v>-3.233898757280147</v>
+        <v>-4.621483400010947</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.3540905319174187</v>
       </c>
       <c r="E88">
-        <v>-18.29122297538747</v>
+        <v>-17.56387107607025</v>
       </c>
       <c r="F88">
-        <v>2.260106705774427</v>
+        <v>0.8030531760898477</v>
       </c>
       <c r="G88">
-        <v>-2.97951302581125</v>
+        <v>-4.868316247377752</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.1064845184479042</v>
       </c>
       <c r="E89">
-        <v>-19.71851973248938</v>
+        <v>-19.60522428075938</v>
       </c>
       <c r="F89">
-        <v>2.124226287223613</v>
+        <v>1.069689732437758</v>
       </c>
       <c r="G89">
-        <v>-1.849470504760002</v>
+        <v>-4.21194633898137</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.08677334435600487</v>
       </c>
       <c r="E90">
-        <v>-22.10821523062585</v>
+        <v>-20.89661965689024</v>
       </c>
       <c r="F90">
-        <v>2.54121649738405</v>
+        <v>0.9172055176652308</v>
       </c>
       <c r="G90">
-        <v>-2.725393590290647</v>
+        <v>-3.995168383347461</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.2169770649469558</v>
       </c>
       <c r="E91">
-        <v>-23.58692874392912</v>
+        <v>-22.59824432841972</v>
       </c>
       <c r="F91">
-        <v>2.311491992504886</v>
+        <v>0.8386199588964474</v>
       </c>
       <c r="G91">
-        <v>-2.403031901902934</v>
+        <v>-4.022364509753088</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.2788191252053302</v>
       </c>
       <c r="E92">
-        <v>-25.59325376430465</v>
+        <v>-24.22913565787604</v>
       </c>
       <c r="F92">
-        <v>2.32159807481904</v>
+        <v>0.8624421486661555</v>
       </c>
       <c r="G92">
-        <v>-2.75809055554975</v>
+        <v>-4.33841602846408</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.2717241756270168</v>
       </c>
       <c r="E93">
-        <v>-27.25389869969204</v>
+        <v>-26.44737413288961</v>
       </c>
       <c r="F93">
-        <v>2.272895041738846</v>
+        <v>1.143233847193104</v>
       </c>
       <c r="G93">
-        <v>-2.526504456595046</v>
+        <v>-4.155987639415448</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.1983573970378421</v>
       </c>
       <c r="E94">
-        <v>-28.71117541274222</v>
+        <v>-28.09501536361897</v>
       </c>
       <c r="F94">
-        <v>2.343137284026632</v>
+        <v>1.303609089844699</v>
       </c>
       <c r="G94">
-        <v>-2.235724945526031</v>
+        <v>-4.240946489899457</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.06679793974840514</v>
       </c>
       <c r="E95">
-        <v>-30.2220991564752</v>
+        <v>-31.3432128682881</v>
       </c>
       <c r="F95">
-        <v>2.109385256835057</v>
+        <v>1.242835086970911</v>
       </c>
       <c r="G95">
-        <v>-2.170495491917066</v>
+        <v>-4.621945501803574</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.1123774587515758</v>
       </c>
       <c r="E96">
-        <v>-34.06123841110323</v>
+        <v>-33.18317477923063</v>
       </c>
       <c r="F96">
-        <v>2.110892885508152</v>
+        <v>1.36542517891121</v>
       </c>
       <c r="G96">
-        <v>-2.311389545265676</v>
+        <v>-4.793758603344739</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.3246405322824759</v>
       </c>
       <c r="E97">
-        <v>-35.86669544235907</v>
+        <v>-34.96670285469138</v>
       </c>
       <c r="F97">
-        <v>2.14269556683643</v>
+        <v>1.295239265606813</v>
       </c>
       <c r="G97">
-        <v>-2.96863144235549</v>
+        <v>-5.042087407362253</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.5590073669757779</v>
       </c>
       <c r="E98">
-        <v>-39.20715446000361</v>
+        <v>-37.56661314403405</v>
       </c>
       <c r="F98">
-        <v>1.869133859001116</v>
+        <v>1.401540340938463</v>
       </c>
       <c r="G98">
-        <v>-3.402879200939954</v>
+        <v>-5.176214410730698</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.7951487139400035</v>
       </c>
       <c r="E99">
-        <v>-41.1774856744325</v>
+        <v>-39.52894112024</v>
       </c>
       <c r="F99">
-        <v>1.867294883366901</v>
+        <v>1.566002748355471</v>
       </c>
       <c r="G99">
-        <v>-3.933152756330156</v>
+        <v>-5.241250669239921</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.025608887813684</v>
       </c>
       <c r="E100">
-        <v>-43.1189873724501</v>
+        <v>-42.4214139983319</v>
       </c>
       <c r="F100">
-        <v>1.81779661758002</v>
+        <v>1.389789120962349</v>
       </c>
       <c r="G100">
-        <v>-3.866268090650425</v>
+        <v>-5.304480292492094</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.223819479071007</v>
       </c>
       <c r="E101">
-        <v>-45.26682891550783</v>
+        <v>-44.44224203265372</v>
       </c>
       <c r="F101">
-        <v>1.711202300187779</v>
+        <v>1.437241319264316</v>
       </c>
       <c r="G101">
-        <v>-3.77015613927318</v>
+        <v>-5.692888597545791</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.39824005309448</v>
       </c>
       <c r="E102">
-        <v>-48.37865780293188</v>
+        <v>-47.25021055822217</v>
       </c>
       <c r="F102">
-        <v>1.499930507573377</v>
+        <v>1.546973492378361</v>
       </c>
       <c r="G102">
-        <v>-4.182716442539266</v>
+        <v>-5.956931473257215</v>
       </c>
     </row>
   </sheetData>
